--- a/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M36B2_IN_Piura.xlsx
+++ b/plantillas_117_msavi_v6/Plantilla_Excel_Bloque_M36B2_IN_Piura.xlsx
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C10" s="19">
         <f>ROUND(B10/$B$15*100,2)</f>
-        <v/>
+        <v>38.47</v>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="C11" s="29">
         <f>ROUND(B11/$B$15*100,2)</f>
-        <v/>
+        <v>56.56</v>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C12" s="19">
         <f>ROUND(B12/$B$15*100,2)</f>
-        <v/>
+        <v>4.3</v>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C13" s="21">
         <f>ROUND(B13/$B$15*100,2)</f>
-        <v/>
+        <v>0.67</v>
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="C14" s="19">
         <f>ROUND(B14/$B$15*100,2)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
@@ -1910,11 +1910,11 @@
       </c>
       <c r="B15" s="43">
         <f>SUM(B10:B14)</f>
-        <v/>
+        <v>28.1903</v>
       </c>
       <c r="C15" s="44">
         <f>SUM(C10:C14)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
@@ -1935,11 +1935,11 @@
       </c>
       <c r="B16" s="46">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>26.7889</v>
       </c>
       <c r="C16" s="47">
         <f>ROUND(B16/B15*100,2)</f>
-        <v/>
+        <v>95.03</v>
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
@@ -1960,11 +1960,11 @@
       </c>
       <c r="B17" s="46">
         <f>SUM(B12:B14)</f>
-        <v/>
+        <v>1.4014</v>
       </c>
       <c r="C17" s="47">
         <f>ROUND(B17/B15*100,2)</f>
-        <v/>
+        <v>4.97</v>
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
@@ -2158,11 +2158,11 @@
       </c>
       <c r="B29" s="22">
         <f>SUM(B25:B28)</f>
-        <v/>
+        <v>28.2017</v>
       </c>
       <c r="C29" s="23">
         <f>SUM(C25:C28)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D29" s="17" t="inlineStr"/>
       <c r="E29" s="17" t="inlineStr"/>
@@ -2281,6 +2281,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
@@ -2574,6 +2575,7 @@
       <c r="F18" s="17" t="inlineStr"/>
       <c r="G18" s="17" t="inlineStr"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
@@ -2618,6 +2620,7 @@
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23" ht="132" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
@@ -2837,11 +2840,11 @@
       </c>
       <c r="B12" s="32">
         <f>SUM(B10:B11)</f>
-        <v/>
+        <v>53.86</v>
       </c>
       <c r="C12" s="23">
         <f>SUM(C10:C11)</f>
-        <v/>
+        <v>100.0</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -2851,19 +2854,19 @@
       <c r="E12" s="17" t="inlineStr"/>
       <c r="F12" s="17">
         <f>ROUND(AVERAGE(F10:F11),2)</f>
-        <v/>
+        <v>30.05</v>
       </c>
       <c r="G12" s="22">
         <f>ROUND(AVERAGE(G10:G11),4)</f>
-        <v/>
+        <v>0.6002</v>
       </c>
       <c r="H12" s="23">
         <f>ROUND(AVERAGE(H10:H11),2)</f>
-        <v/>
+        <v>82.62</v>
       </c>
       <c r="I12" s="23">
         <f>ROUND(AVERAGE(I10:I11),2)</f>
-        <v/>
+        <v>4.78</v>
       </c>
     </row>
     <row r="13"/>
